--- a/Module2/DataEngineeringPandas/Pandas_TV_GTrends_Data.xlsx
+++ b/Module2/DataEngineeringPandas/Pandas_TV_GTrends_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitaetstgallen-my.sharepoint.com/personal/ivo_blohm_unisg_ch/Documents/Lehre/CAS/Delivery/2020_2021/Module2/04_DataEngineeringPandas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universitaetstgallen.sharepoint.com/sites/o365-iwi-iwi7/Freigegebene Dokumente/Executive Education/CAS/2026/12_Module_2/02_AnalyticsPlattform/pandas_acm_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_6827EABD737B87C14B228F1F190F4B857443B70E" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{668A507E-631E-442A-88F1-085F7A42D2CD}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_6827EABD737B87C14B228F1F190F4B857443B70E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F02788C-5680-2940-AA9B-FCB1ECB5E066}"/>
   <bookViews>
-    <workbookView xWindow="1332" yWindow="-108" windowWidth="21816" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4380" yWindow="580" windowWidth="21820" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="9">
   <si>
     <t>date</t>
-  </si>
-  <si>
-    <t>IndustryAdType</t>
   </si>
   <si>
     <t>GTrend</t>
@@ -48,15 +45,18 @@
   <si>
     <t>Home Cleaning Product</t>
   </si>
+  <si>
+    <t>Industry_Ad_Type</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,6 +68,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,10 +111,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -414,5220 +415,5222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C474"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>43568</v>
+        <v>45029</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>43568</v>
+        <v>45029</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>43568</v>
+        <v>45029</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>43568</v>
+        <v>45029</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>43568</v>
+        <v>45029</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>43575</v>
+        <v>45036</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>43575</v>
+        <v>45036</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>43575</v>
+        <v>45036</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>43575</v>
+        <v>45036</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>43582</v>
+        <v>45043</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>43582</v>
+        <v>45043</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>43582</v>
+        <v>45043</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>43589</v>
+        <v>45050</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>43589</v>
+        <v>45050</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>43589</v>
+        <v>45050</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>43589</v>
+        <v>45050</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>43596</v>
+        <v>45057</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>43596</v>
+        <v>45057</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>43596</v>
+        <v>45057</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>43596</v>
+        <v>45057</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>43603</v>
+        <v>45064</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>43603</v>
+        <v>45064</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>43603</v>
+        <v>45064</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>43603</v>
+        <v>45064</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>43610</v>
+        <v>45071</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>43610</v>
+        <v>45071</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>43610</v>
+        <v>45071</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28">
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>43617</v>
+        <v>45078</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>43617</v>
+        <v>45078</v>
       </c>
       <c r="B30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>43617</v>
+        <v>45078</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>43617</v>
+        <v>45078</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>43624</v>
+        <v>45085</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>74</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>43624</v>
+        <v>45085</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>43624</v>
+        <v>45085</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>43624</v>
+        <v>45085</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>43631</v>
+        <v>45092</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>43631</v>
+        <v>45092</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38">
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>43631</v>
+        <v>45092</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>43631</v>
+        <v>45092</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40">
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>43638</v>
+        <v>45099</v>
       </c>
       <c r="B41" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>43638</v>
+        <v>45099</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>43638</v>
+        <v>45099</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>43638</v>
+        <v>45099</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>43645</v>
+        <v>45106</v>
       </c>
       <c r="B45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45">
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>43645</v>
+        <v>45106</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>53</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>43645</v>
+        <v>45106</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>43645</v>
+        <v>45106</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48">
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>43652</v>
+        <v>45113</v>
       </c>
       <c r="B49" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>43652</v>
+        <v>45113</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>43652</v>
+        <v>45113</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51">
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>43652</v>
+        <v>45113</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>43659</v>
+        <v>45120</v>
       </c>
       <c r="B53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>43659</v>
+        <v>45120</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>43659</v>
+        <v>45120</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55">
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>43659</v>
+        <v>45120</v>
       </c>
       <c r="B56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56">
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>43666</v>
+        <v>45127</v>
       </c>
       <c r="B57" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57">
         <v>75</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>43666</v>
+        <v>45127</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>43666</v>
+        <v>45127</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59">
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>43666</v>
+        <v>45127</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C60">
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>43673</v>
+        <v>45134</v>
       </c>
       <c r="B61" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>43673</v>
+        <v>45134</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>52</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>43673</v>
+        <v>45134</v>
       </c>
       <c r="B63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63">
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>43673</v>
+        <v>45134</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64">
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>43680</v>
+        <v>45141</v>
       </c>
       <c r="B65" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>43680</v>
+        <v>45141</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>43680</v>
+        <v>45141</v>
       </c>
       <c r="B67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>43680</v>
+        <v>45141</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>43680</v>
+        <v>45141</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C69">
         <v>64</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>43687</v>
+        <v>45148</v>
       </c>
       <c r="B70" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>43687</v>
+        <v>45148</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>55</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>43687</v>
+        <v>45148</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>43687</v>
+        <v>45148</v>
       </c>
       <c r="B73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73">
         <v>68</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>43694</v>
+        <v>45155</v>
       </c>
       <c r="B74" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>43694</v>
+        <v>45155</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75">
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>43694</v>
+        <v>45155</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>43694</v>
+        <v>45155</v>
       </c>
       <c r="B77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77">
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>43701</v>
+        <v>45162</v>
       </c>
       <c r="B78" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>43701</v>
+        <v>45162</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>52</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>43701</v>
+        <v>45162</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80">
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>43701</v>
+        <v>45162</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>43708</v>
+        <v>45169</v>
       </c>
       <c r="B82" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>43708</v>
+        <v>45169</v>
       </c>
       <c r="B83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83">
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>43708</v>
+        <v>45169</v>
       </c>
       <c r="B84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C84">
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>43715</v>
+        <v>45176</v>
       </c>
       <c r="B85" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>60</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>43715</v>
+        <v>45176</v>
       </c>
       <c r="B86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86">
         <v>54</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>43715</v>
+        <v>45176</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87">
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>43715</v>
+        <v>45176</v>
       </c>
       <c r="B88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88">
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>43722</v>
+        <v>45183</v>
       </c>
       <c r="B89" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>38</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>43722</v>
+        <v>45183</v>
       </c>
       <c r="B90" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90">
         <v>54</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>43722</v>
+        <v>45183</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91">
         <v>55</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>43722</v>
+        <v>45183</v>
       </c>
       <c r="B92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C92">
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>43729</v>
+        <v>45190</v>
       </c>
       <c r="B93" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>43729</v>
+        <v>45190</v>
       </c>
       <c r="B94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94">
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>43729</v>
+        <v>45190</v>
       </c>
       <c r="B95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95">
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>43729</v>
+        <v>45190</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96">
         <v>52</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>43729</v>
+        <v>45190</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C97">
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>43736</v>
+        <v>45197</v>
       </c>
       <c r="B98" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>43736</v>
+        <v>45197</v>
       </c>
       <c r="B99" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C99">
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>43736</v>
+        <v>45197</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100">
         <v>52</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>43736</v>
+        <v>45197</v>
       </c>
       <c r="B101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101">
         <v>60</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>43743</v>
+        <v>45204</v>
       </c>
       <c r="B102" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102">
         <v>37</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>43743</v>
+        <v>45204</v>
       </c>
       <c r="B103" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103">
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>43743</v>
+        <v>45204</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104">
         <v>49</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>43743</v>
+        <v>45204</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105">
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>43743</v>
+        <v>45204</v>
       </c>
       <c r="B106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C106">
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>43750</v>
+        <v>45211</v>
       </c>
       <c r="B107" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>49</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>43750</v>
+        <v>45211</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108">
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>43750</v>
+        <v>45211</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109">
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>43750</v>
+        <v>45211</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C110">
         <v>60</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>43785</v>
+        <v>45246</v>
       </c>
       <c r="B111" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C111">
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>43785</v>
+        <v>45246</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112">
         <v>45</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>43785</v>
+        <v>45246</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113">
         <v>54</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
-        <v>43785</v>
+        <v>45246</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114">
         <v>54</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
-        <v>43785</v>
+        <v>45246</v>
       </c>
       <c r="B115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C115">
         <v>87</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
-        <v>43792</v>
+        <v>45253</v>
       </c>
       <c r="B116" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
-        <v>43792</v>
+        <v>45253</v>
       </c>
       <c r="B117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117">
         <v>98</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
-        <v>43792</v>
+        <v>45253</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>48</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
-        <v>43792</v>
+        <v>45253</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119">
         <v>83</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
-        <v>43792</v>
+        <v>45253</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120">
         <v>68</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
-        <v>43799</v>
+        <v>45260</v>
       </c>
       <c r="B121" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121">
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
-        <v>43799</v>
+        <v>45260</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122">
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
-        <v>43799</v>
+        <v>45260</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C123">
         <v>65</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
-        <v>43799</v>
+        <v>45260</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124">
         <v>52</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
-        <v>43799</v>
+        <v>45260</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C125">
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
-        <v>43799</v>
+        <v>45260</v>
       </c>
       <c r="B126" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C126">
         <v>54</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
-        <v>43806</v>
+        <v>45267</v>
       </c>
       <c r="B127" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C127">
         <v>48</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
-        <v>43806</v>
+        <v>45267</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128">
         <v>51</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
-        <v>43806</v>
+        <v>45267</v>
       </c>
       <c r="B129" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129">
         <v>60</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
-        <v>43806</v>
+        <v>45267</v>
       </c>
       <c r="B130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
-        <v>43806</v>
+        <v>45267</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131">
         <v>56</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
-        <v>43806</v>
+        <v>45267</v>
       </c>
       <c r="B132" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C132">
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
-        <v>43813</v>
+        <v>45274</v>
       </c>
       <c r="B133" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C133">
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
-        <v>43813</v>
+        <v>45274</v>
       </c>
       <c r="B134" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134">
         <v>49</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
-        <v>43813</v>
+        <v>45274</v>
       </c>
       <c r="B135" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C135">
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
-        <v>43813</v>
+        <v>45274</v>
       </c>
       <c r="B136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136">
         <v>43</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
-        <v>43813</v>
+        <v>45274</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C137">
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
-        <v>43813</v>
+        <v>45274</v>
       </c>
       <c r="B138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C138">
         <v>58</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
-        <v>43820</v>
+        <v>45281</v>
       </c>
       <c r="B139" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C139">
         <v>32</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
-        <v>43820</v>
+        <v>45281</v>
       </c>
       <c r="B140" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C140">
         <v>58</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
-        <v>43820</v>
+        <v>45281</v>
       </c>
       <c r="B141" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C141">
         <v>63</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
-        <v>43820</v>
+        <v>45281</v>
       </c>
       <c r="B142" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C142">
         <v>45</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
-        <v>43820</v>
+        <v>45281</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C143">
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
-        <v>43820</v>
+        <v>45281</v>
       </c>
       <c r="B144" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C144">
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
-        <v>43827</v>
+        <v>45288</v>
       </c>
       <c r="B145" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C145">
         <v>62</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
-        <v>43827</v>
+        <v>45288</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146">
         <v>66</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
-        <v>43827</v>
+        <v>45288</v>
       </c>
       <c r="B147" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C147">
         <v>66</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
-        <v>43834</v>
+        <v>45295</v>
       </c>
       <c r="B148" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148">
         <v>94</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
-        <v>43834</v>
+        <v>45295</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C149">
         <v>52</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
-        <v>43834</v>
+        <v>45295</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C150">
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
-        <v>43834</v>
+        <v>45295</v>
       </c>
       <c r="B151" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C151">
         <v>64</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
-        <v>43841</v>
+        <v>45302</v>
       </c>
       <c r="B152" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C152">
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
-        <v>43841</v>
+        <v>45302</v>
       </c>
       <c r="B153" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153">
         <v>57</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
-        <v>43841</v>
+        <v>45302</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C154">
         <v>47</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
-        <v>43841</v>
+        <v>45302</v>
       </c>
       <c r="B155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C155">
         <v>64</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
-        <v>43848</v>
+        <v>45309</v>
       </c>
       <c r="B156" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156">
         <v>62</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
-        <v>43848</v>
+        <v>45309</v>
       </c>
       <c r="B157" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C157">
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
-        <v>43848</v>
+        <v>45309</v>
       </c>
       <c r="B158" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158">
         <v>52</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
-        <v>43848</v>
+        <v>45309</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159">
         <v>51</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
-        <v>43848</v>
+        <v>45309</v>
       </c>
       <c r="B160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C160">
         <v>66</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
-        <v>43855</v>
+        <v>45316</v>
       </c>
       <c r="B161" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C161">
         <v>71</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
-        <v>43855</v>
+        <v>45316</v>
       </c>
       <c r="B162" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C162">
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
-        <v>43855</v>
+        <v>45316</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163">
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
-        <v>43855</v>
+        <v>45316</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C164">
         <v>45</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
-        <v>43855</v>
+        <v>45316</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C165">
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
-        <v>43862</v>
+        <v>45323</v>
       </c>
       <c r="B166" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C166">
         <v>72</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
-        <v>43862</v>
+        <v>45323</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C167">
         <v>46</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
-        <v>43862</v>
+        <v>45323</v>
       </c>
       <c r="B168" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C168">
         <v>74</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
-        <v>43869</v>
+        <v>45330</v>
       </c>
       <c r="B169" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C169">
         <v>63</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
-        <v>43869</v>
+        <v>45330</v>
       </c>
       <c r="B170" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C170">
         <v>37</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
-        <v>43869</v>
+        <v>45330</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171">
         <v>58</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
-        <v>43869</v>
+        <v>45330</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C172">
         <v>54</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
-        <v>43869</v>
+        <v>45330</v>
       </c>
       <c r="B173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C173">
         <v>63</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
-        <v>43876</v>
+        <v>45337</v>
       </c>
       <c r="B174" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C174">
         <v>74</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
-        <v>43876</v>
+        <v>45337</v>
       </c>
       <c r="B175" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C175">
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
-        <v>43876</v>
+        <v>45337</v>
       </c>
       <c r="B176" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C176">
         <v>63</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
-        <v>43876</v>
+        <v>45337</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C177">
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
-        <v>43876</v>
+        <v>45337</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C178">
         <v>55</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
-        <v>43876</v>
+        <v>45337</v>
       </c>
       <c r="B179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C179">
         <v>65</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
-        <v>43883</v>
+        <v>45344</v>
       </c>
       <c r="B180" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C180">
         <v>50</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
-        <v>43883</v>
+        <v>45344</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181">
         <v>55</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
-        <v>43883</v>
+        <v>45344</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C182">
         <v>51</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
-        <v>43883</v>
+        <v>45344</v>
       </c>
       <c r="B183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C183">
         <v>66</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
-        <v>43890</v>
+        <v>45351</v>
       </c>
       <c r="B184" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C184">
         <v>79</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
-        <v>43890</v>
+        <v>45351</v>
       </c>
       <c r="B185" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C185">
         <v>53</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
-        <v>43890</v>
+        <v>45351</v>
       </c>
       <c r="B186" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C186">
         <v>48</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
-        <v>43890</v>
+        <v>45351</v>
       </c>
       <c r="B187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C187">
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
-        <v>43897</v>
+        <v>45358</v>
       </c>
       <c r="B188" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C188">
         <v>54</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
-        <v>43897</v>
+        <v>45358</v>
       </c>
       <c r="B189" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C189">
         <v>55</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
-        <v>43897</v>
+        <v>45358</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C190">
         <v>45</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
-        <v>43897</v>
+        <v>45358</v>
       </c>
       <c r="B191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C191">
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
-        <v>43904</v>
+        <v>45365</v>
       </c>
       <c r="B192" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C192">
         <v>27</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
-        <v>43904</v>
+        <v>45365</v>
       </c>
       <c r="B193" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C193">
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
-        <v>43904</v>
+        <v>45365</v>
       </c>
       <c r="B194" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C194">
         <v>29</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
-        <v>43904</v>
+        <v>45365</v>
       </c>
       <c r="B195" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C195">
         <v>38</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
-        <v>43911</v>
+        <v>45372</v>
       </c>
       <c r="B196" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C196">
         <v>10</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
-        <v>43911</v>
+        <v>45372</v>
       </c>
       <c r="B197" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C197">
         <v>59</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
-        <v>43911</v>
+        <v>45372</v>
       </c>
       <c r="B198" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>41</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
-        <v>43911</v>
+        <v>45372</v>
       </c>
       <c r="B199" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C199">
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
-        <v>43911</v>
+        <v>45372</v>
       </c>
       <c r="B200" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C200">
         <v>36</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
-        <v>43918</v>
+        <v>45379</v>
       </c>
       <c r="B201" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C201">
         <v>11</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
-        <v>43918</v>
+        <v>45379</v>
       </c>
       <c r="B202" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C202">
         <v>70</v>
       </c>
     </row>
-    <row r="203" spans="1:3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
-        <v>43918</v>
+        <v>45379</v>
       </c>
       <c r="B203" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203">
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
-        <v>43918</v>
+        <v>45379</v>
       </c>
       <c r="B204" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C204">
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
-        <v>43918</v>
+        <v>45379</v>
       </c>
       <c r="B205" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C205">
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
-        <v>43925</v>
+        <v>45386</v>
       </c>
       <c r="B206" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C206">
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
-        <v>43925</v>
+        <v>45386</v>
       </c>
       <c r="B207" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C207">
         <v>69</v>
       </c>
     </row>
-    <row r="208" spans="1:3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
-        <v>43925</v>
+        <v>45386</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C208">
         <v>44</v>
       </c>
     </row>
-    <row r="209" spans="1:3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
-        <v>43925</v>
+        <v>45386</v>
       </c>
       <c r="B209" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C209">
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:3">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
-        <v>43925</v>
+        <v>45386</v>
       </c>
       <c r="B210" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C210">
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="1:3">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
-        <v>43932</v>
+        <v>45393</v>
       </c>
       <c r="B211" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C211">
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
-        <v>43932</v>
+        <v>45393</v>
       </c>
       <c r="B212" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C212">
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
-        <v>43932</v>
+        <v>45393</v>
       </c>
       <c r="B213" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C213">
         <v>39</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
-        <v>43939</v>
+        <v>45400</v>
       </c>
       <c r="B214" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C214">
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
-        <v>43939</v>
+        <v>45400</v>
       </c>
       <c r="B215" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C215">
         <v>63</v>
       </c>
     </row>
-    <row r="216" spans="1:3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
-        <v>43939</v>
+        <v>45400</v>
       </c>
       <c r="B216" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C216">
         <v>37</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
-        <v>43939</v>
+        <v>45400</v>
       </c>
       <c r="B217" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C217">
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
-        <v>43939</v>
+        <v>45400</v>
       </c>
       <c r="B218" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C218">
         <v>42</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
-        <v>43946</v>
+        <v>45407</v>
       </c>
       <c r="B219" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C219">
         <v>5</v>
       </c>
     </row>
-    <row r="220" spans="1:3">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
-        <v>43946</v>
+        <v>45407</v>
       </c>
       <c r="B220" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C220">
         <v>58</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
-        <v>43946</v>
+        <v>45407</v>
       </c>
       <c r="B221" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C221">
         <v>41</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
-        <v>43946</v>
+        <v>45407</v>
       </c>
       <c r="B222" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C222">
         <v>16</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
-        <v>43946</v>
+        <v>45407</v>
       </c>
       <c r="B223" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C223">
         <v>44</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
-        <v>43953</v>
+        <v>45414</v>
       </c>
       <c r="B224" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C224">
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
-        <v>43953</v>
+        <v>45414</v>
       </c>
       <c r="B225" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C225">
         <v>12</v>
       </c>
     </row>
-    <row r="226" spans="1:3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
-        <v>43953</v>
+        <v>45414</v>
       </c>
       <c r="B226" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C226">
         <v>49</v>
       </c>
     </row>
-    <row r="227" spans="1:3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
-        <v>43960</v>
+        <v>45421</v>
       </c>
       <c r="B227" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
-        <v>43960</v>
+        <v>45421</v>
       </c>
       <c r="B228" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C228">
         <v>77</v>
       </c>
     </row>
-    <row r="229" spans="1:3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
-        <v>43960</v>
+        <v>45421</v>
       </c>
       <c r="B229" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229">
         <v>38</v>
       </c>
     </row>
-    <row r="230" spans="1:3">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
-        <v>43960</v>
+        <v>45421</v>
       </c>
       <c r="B230" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C230">
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="1:3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
-        <v>43960</v>
+        <v>45421</v>
       </c>
       <c r="B231" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C231">
         <v>54</v>
       </c>
     </row>
-    <row r="232" spans="1:3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
-        <v>43967</v>
+        <v>45428</v>
       </c>
       <c r="B232" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C232">
         <v>20</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
-        <v>43967</v>
+        <v>45428</v>
       </c>
       <c r="B233" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C233">
         <v>41</v>
       </c>
     </row>
-    <row r="234" spans="1:3">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
-        <v>43967</v>
+        <v>45428</v>
       </c>
       <c r="B234" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C234">
         <v>77</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
-        <v>43967</v>
+        <v>45428</v>
       </c>
       <c r="B235" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235">
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
-        <v>43967</v>
+        <v>45428</v>
       </c>
       <c r="B236" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C236">
         <v>13</v>
       </c>
     </row>
-    <row r="237" spans="1:3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
-        <v>43967</v>
+        <v>45428</v>
       </c>
       <c r="B237" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C237">
         <v>57</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
-        <v>43981</v>
+        <v>45442</v>
       </c>
       <c r="B238" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C238">
         <v>53</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
-        <v>43981</v>
+        <v>45442</v>
       </c>
       <c r="B239" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C239">
         <v>34</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
-        <v>43981</v>
+        <v>45442</v>
       </c>
       <c r="B240" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240">
         <v>51</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
-        <v>43981</v>
+        <v>45442</v>
       </c>
       <c r="B241" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C241">
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
-        <v>43981</v>
+        <v>45442</v>
       </c>
       <c r="B242" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C242">
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
-        <v>43988</v>
+        <v>45449</v>
       </c>
       <c r="B243" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C243">
         <v>71</v>
       </c>
     </row>
-    <row r="244" spans="1:3">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
-        <v>43988</v>
+        <v>45449</v>
       </c>
       <c r="B244" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C244">
         <v>71</v>
       </c>
     </row>
-    <row r="245" spans="1:3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
-        <v>43988</v>
+        <v>45449</v>
       </c>
       <c r="B245" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C245">
         <v>62</v>
       </c>
     </row>
-    <row r="246" spans="1:3">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
-        <v>43988</v>
+        <v>45449</v>
       </c>
       <c r="B246" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C246">
         <v>27</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
-        <v>43988</v>
+        <v>45449</v>
       </c>
       <c r="B247" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C247">
         <v>64</v>
       </c>
     </row>
-    <row r="248" spans="1:3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
-        <v>43995</v>
+        <v>45456</v>
       </c>
       <c r="B248" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C248">
         <v>54</v>
       </c>
     </row>
-    <row r="249" spans="1:3">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
-        <v>43995</v>
+        <v>45456</v>
       </c>
       <c r="B249" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C249">
         <v>84</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
-        <v>43995</v>
+        <v>45456</v>
       </c>
       <c r="B250" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C250">
         <v>34</v>
       </c>
     </row>
-    <row r="251" spans="1:3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
-        <v>43995</v>
+        <v>45456</v>
       </c>
       <c r="B251" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C251">
         <v>70</v>
       </c>
     </row>
-    <row r="252" spans="1:3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
-        <v>44002</v>
+        <v>45463</v>
       </c>
       <c r="B252" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C252">
         <v>52</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
-        <v>44002</v>
+        <v>45463</v>
       </c>
       <c r="B253" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C253">
         <v>74</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
-        <v>44002</v>
+        <v>45463</v>
       </c>
       <c r="B254" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C254">
         <v>53</v>
       </c>
     </row>
-    <row r="255" spans="1:3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
-        <v>44002</v>
+        <v>45463</v>
       </c>
       <c r="B255" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C255">
         <v>45</v>
       </c>
     </row>
-    <row r="256" spans="1:3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
-        <v>44002</v>
+        <v>45463</v>
       </c>
       <c r="B256" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C256">
         <v>70</v>
       </c>
     </row>
-    <row r="257" spans="1:3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
-        <v>44009</v>
+        <v>45470</v>
       </c>
       <c r="B257" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C257">
         <v>62</v>
       </c>
     </row>
-    <row r="258" spans="1:3">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
-        <v>44009</v>
+        <v>45470</v>
       </c>
       <c r="B258" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C258">
         <v>72</v>
       </c>
     </row>
-    <row r="259" spans="1:3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
-        <v>44009</v>
+        <v>45470</v>
       </c>
       <c r="B259" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C259">
         <v>50</v>
       </c>
     </row>
-    <row r="260" spans="1:3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
-        <v>44009</v>
+        <v>45470</v>
       </c>
       <c r="B260" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C260">
         <v>46</v>
       </c>
     </row>
-    <row r="261" spans="1:3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
-        <v>44009</v>
+        <v>45470</v>
       </c>
       <c r="B261" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C261">
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
-        <v>44016</v>
+        <v>45477</v>
       </c>
       <c r="B262" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C262">
         <v>52</v>
       </c>
     </row>
-    <row r="263" spans="1:3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
-        <v>44016</v>
+        <v>45477</v>
       </c>
       <c r="B263" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C263">
         <v>73</v>
       </c>
     </row>
-    <row r="264" spans="1:3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
-        <v>44016</v>
+        <v>45477</v>
       </c>
       <c r="B264" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C264">
         <v>43</v>
       </c>
     </row>
-    <row r="265" spans="1:3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
-        <v>44016</v>
+        <v>45477</v>
       </c>
       <c r="B265" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C265">
         <v>41</v>
       </c>
     </row>
-    <row r="266" spans="1:3">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
-        <v>44016</v>
+        <v>45477</v>
       </c>
       <c r="B266" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C266">
         <v>69</v>
       </c>
     </row>
-    <row r="267" spans="1:3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
-        <v>44023</v>
+        <v>45484</v>
       </c>
       <c r="B267" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C267">
         <v>52</v>
       </c>
     </row>
-    <row r="268" spans="1:3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
-        <v>44023</v>
+        <v>45484</v>
       </c>
       <c r="B268" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C268">
         <v>79</v>
       </c>
     </row>
-    <row r="269" spans="1:3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
-        <v>44023</v>
+        <v>45484</v>
       </c>
       <c r="B269" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C269">
         <v>38</v>
       </c>
     </row>
-    <row r="270" spans="1:3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
-        <v>44023</v>
+        <v>45484</v>
       </c>
       <c r="B270" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C270">
         <v>71</v>
       </c>
     </row>
-    <row r="271" spans="1:3">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
-        <v>44030</v>
+        <v>45491</v>
       </c>
       <c r="B271" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C271">
         <v>64</v>
       </c>
     </row>
-    <row r="272" spans="1:3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
-        <v>44030</v>
+        <v>45491</v>
       </c>
       <c r="B272" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C272">
         <v>72</v>
       </c>
     </row>
-    <row r="273" spans="1:3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
-        <v>44030</v>
+        <v>45491</v>
       </c>
       <c r="B273" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C273">
         <v>50</v>
       </c>
     </row>
-    <row r="274" spans="1:3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
-        <v>44030</v>
+        <v>45491</v>
       </c>
       <c r="B274" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C274">
         <v>38</v>
       </c>
     </row>
-    <row r="275" spans="1:3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
-        <v>44030</v>
+        <v>45491</v>
       </c>
       <c r="B275" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C275">
         <v>74</v>
       </c>
     </row>
-    <row r="276" spans="1:3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
-        <v>44037</v>
+        <v>45498</v>
       </c>
       <c r="B276" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C276">
         <v>56</v>
       </c>
     </row>
-    <row r="277" spans="1:3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
-        <v>44037</v>
+        <v>45498</v>
       </c>
       <c r="B277" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C277">
         <v>75</v>
       </c>
     </row>
-    <row r="278" spans="1:3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
-        <v>44037</v>
+        <v>45498</v>
       </c>
       <c r="B278" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C278">
         <v>48</v>
       </c>
     </row>
-    <row r="279" spans="1:3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
-        <v>44037</v>
+        <v>45498</v>
       </c>
       <c r="B279" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C279">
         <v>38</v>
       </c>
     </row>
-    <row r="280" spans="1:3">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
-        <v>44037</v>
+        <v>45498</v>
       </c>
       <c r="B280" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C280">
         <v>72</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
-        <v>44044</v>
+        <v>45505</v>
       </c>
       <c r="B281" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C281">
         <v>53</v>
       </c>
     </row>
-    <row r="282" spans="1:3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
-        <v>44044</v>
+        <v>45505</v>
       </c>
       <c r="B282" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C282">
         <v>74</v>
       </c>
     </row>
-    <row r="283" spans="1:3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
-        <v>44044</v>
+        <v>45505</v>
       </c>
       <c r="B283" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C283">
         <v>46</v>
       </c>
     </row>
-    <row r="284" spans="1:3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
-        <v>44044</v>
+        <v>45505</v>
       </c>
       <c r="B284" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C284">
         <v>42</v>
       </c>
     </row>
-    <row r="285" spans="1:3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
-        <v>44044</v>
+        <v>45505</v>
       </c>
       <c r="B285" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C285">
         <v>68</v>
       </c>
     </row>
-    <row r="286" spans="1:3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
-        <v>44051</v>
+        <v>45512</v>
       </c>
       <c r="B286" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C286">
         <v>75</v>
       </c>
     </row>
-    <row r="287" spans="1:3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
-        <v>44051</v>
+        <v>45512</v>
       </c>
       <c r="B287" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C287">
         <v>71</v>
       </c>
     </row>
-    <row r="288" spans="1:3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
-        <v>44051</v>
+        <v>45512</v>
       </c>
       <c r="B288" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C288">
         <v>48</v>
       </c>
     </row>
-    <row r="289" spans="1:3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
-        <v>44051</v>
+        <v>45512</v>
       </c>
       <c r="B289" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C289">
         <v>68</v>
       </c>
     </row>
-    <row r="290" spans="1:3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
-        <v>44058</v>
+        <v>45519</v>
       </c>
       <c r="B290" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C290">
         <v>42</v>
       </c>
     </row>
-    <row r="291" spans="1:3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
-        <v>44058</v>
+        <v>45519</v>
       </c>
       <c r="B291" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C291">
         <v>68</v>
       </c>
     </row>
-    <row r="292" spans="1:3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
-        <v>44058</v>
+        <v>45519</v>
       </c>
       <c r="B292" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292">
         <v>47</v>
       </c>
     </row>
-    <row r="293" spans="1:3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
-        <v>44058</v>
+        <v>45519</v>
       </c>
       <c r="B293" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C293">
         <v>38</v>
       </c>
     </row>
-    <row r="294" spans="1:3">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
-        <v>44058</v>
+        <v>45519</v>
       </c>
       <c r="B294" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C294">
         <v>69</v>
       </c>
     </row>
-    <row r="295" spans="1:3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
-        <v>44065</v>
+        <v>45526</v>
       </c>
       <c r="B295" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C295">
         <v>57</v>
       </c>
     </row>
-    <row r="296" spans="1:3">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
-        <v>44065</v>
+        <v>45526</v>
       </c>
       <c r="B296" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C296">
         <v>50</v>
       </c>
     </row>
-    <row r="297" spans="1:3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
-        <v>44065</v>
+        <v>45526</v>
       </c>
       <c r="B297" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C297">
         <v>47</v>
       </c>
     </row>
-    <row r="298" spans="1:3">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
-        <v>44065</v>
+        <v>45526</v>
       </c>
       <c r="B298" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C298">
         <v>66</v>
       </c>
     </row>
-    <row r="299" spans="1:3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
-        <v>44072</v>
+        <v>45533</v>
       </c>
       <c r="B299" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C299">
         <v>62</v>
       </c>
     </row>
-    <row r="300" spans="1:3">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
-        <v>44072</v>
+        <v>45533</v>
       </c>
       <c r="B300" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C300">
         <v>74</v>
       </c>
     </row>
-    <row r="301" spans="1:3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
-        <v>44072</v>
+        <v>45533</v>
       </c>
       <c r="B301" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C301">
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:3">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
-        <v>44072</v>
+        <v>45533</v>
       </c>
       <c r="B302" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C302">
         <v>64</v>
       </c>
     </row>
-    <row r="303" spans="1:3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
-        <v>44079</v>
+        <v>45540</v>
       </c>
       <c r="B303" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C303">
         <v>51</v>
       </c>
     </row>
-    <row r="304" spans="1:3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
-        <v>44079</v>
+        <v>45540</v>
       </c>
       <c r="B304" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C304">
         <v>73</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
-        <v>44079</v>
+        <v>45540</v>
       </c>
       <c r="B305" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C305">
         <v>38</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
-        <v>44079</v>
+        <v>45540</v>
       </c>
       <c r="B306" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C306">
         <v>43</v>
       </c>
     </row>
-    <row r="307" spans="1:3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
-        <v>44079</v>
+        <v>45540</v>
       </c>
       <c r="B307" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C307">
         <v>63</v>
       </c>
     </row>
-    <row r="308" spans="1:3">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
-        <v>44086</v>
+        <v>45547</v>
       </c>
       <c r="B308" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C308">
         <v>50</v>
       </c>
     </row>
-    <row r="309" spans="1:3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
-        <v>44086</v>
+        <v>45547</v>
       </c>
       <c r="B309" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C309">
         <v>74</v>
       </c>
     </row>
-    <row r="310" spans="1:3">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
-        <v>44086</v>
+        <v>45547</v>
       </c>
       <c r="B310" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310">
         <v>44</v>
       </c>
     </row>
-    <row r="311" spans="1:3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
-        <v>44086</v>
+        <v>45547</v>
       </c>
       <c r="B311" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C311">
         <v>38</v>
       </c>
     </row>
-    <row r="312" spans="1:3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
-        <v>44086</v>
+        <v>45547</v>
       </c>
       <c r="B312" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C312">
         <v>62</v>
       </c>
     </row>
-    <row r="313" spans="1:3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
-        <v>44093</v>
+        <v>45554</v>
       </c>
       <c r="B313" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C313">
         <v>55</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" s="2">
-        <v>44093</v>
+        <v>45554</v>
       </c>
       <c r="B314" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C314">
         <v>38</v>
       </c>
     </row>
-    <row r="315" spans="1:3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" s="2">
-        <v>44093</v>
+        <v>45554</v>
       </c>
       <c r="B315" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C315">
         <v>38</v>
       </c>
     </row>
-    <row r="316" spans="1:3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" s="2">
-        <v>44093</v>
+        <v>45554</v>
       </c>
       <c r="B316" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C316">
         <v>62</v>
       </c>
     </row>
-    <row r="317" spans="1:3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" s="2">
-        <v>44100</v>
+        <v>45561</v>
       </c>
       <c r="B317" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C317">
         <v>64</v>
       </c>
     </row>
-    <row r="318" spans="1:3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" s="2">
-        <v>44100</v>
+        <v>45561</v>
       </c>
       <c r="B318" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C318">
         <v>33</v>
       </c>
     </row>
-    <row r="319" spans="1:3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" s="2">
-        <v>44100</v>
+        <v>45561</v>
       </c>
       <c r="B319" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C319">
         <v>60</v>
       </c>
     </row>
-    <row r="320" spans="1:3">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" s="2">
-        <v>44107</v>
+        <v>45568</v>
       </c>
       <c r="B320" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C320">
         <v>56</v>
       </c>
     </row>
-    <row r="321" spans="1:3">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="2">
-        <v>44107</v>
+        <v>45568</v>
       </c>
       <c r="B321" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C321">
         <v>72</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" s="2">
-        <v>44107</v>
+        <v>45568</v>
       </c>
       <c r="B322" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C322">
         <v>36</v>
       </c>
     </row>
-    <row r="323" spans="1:3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" s="2">
-        <v>44107</v>
+        <v>45568</v>
       </c>
       <c r="B323" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C323">
         <v>40</v>
       </c>
     </row>
-    <row r="324" spans="1:3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" s="2">
-        <v>44107</v>
+        <v>45568</v>
       </c>
       <c r="B324" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C324">
         <v>62</v>
       </c>
     </row>
-    <row r="325" spans="1:3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" s="2">
-        <v>44114</v>
+        <v>45575</v>
       </c>
       <c r="B325" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C325">
         <v>41</v>
       </c>
     </row>
-    <row r="326" spans="1:3">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
-        <v>44114</v>
+        <v>45575</v>
       </c>
       <c r="B326" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C326">
         <v>44</v>
       </c>
     </row>
-    <row r="327" spans="1:3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
-        <v>44114</v>
+        <v>45575</v>
       </c>
       <c r="B327" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C327">
         <v>76</v>
       </c>
     </row>
-    <row r="328" spans="1:3">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
-        <v>44114</v>
+        <v>45575</v>
       </c>
       <c r="B328" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C328">
         <v>41</v>
       </c>
     </row>
-    <row r="329" spans="1:3">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
-        <v>44114</v>
+        <v>45575</v>
       </c>
       <c r="B329" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C329">
         <v>45</v>
       </c>
     </row>
-    <row r="330" spans="1:3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
-        <v>44114</v>
+        <v>45575</v>
       </c>
       <c r="B330" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C330">
         <v>63</v>
       </c>
     </row>
-    <row r="331" spans="1:3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
-        <v>44121</v>
+        <v>45582</v>
       </c>
       <c r="B331" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C331">
         <v>50</v>
       </c>
     </row>
-    <row r="332" spans="1:3">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
-        <v>44121</v>
+        <v>45582</v>
       </c>
       <c r="B332" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C332">
         <v>35</v>
       </c>
     </row>
-    <row r="333" spans="1:3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
-        <v>44121</v>
+        <v>45582</v>
       </c>
       <c r="B333" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C333">
         <v>71</v>
       </c>
     </row>
-    <row r="334" spans="1:3">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
-        <v>44121</v>
+        <v>45582</v>
       </c>
       <c r="B334" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C334">
         <v>39</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
-        <v>44121</v>
+        <v>45582</v>
       </c>
       <c r="B335" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C335">
         <v>68</v>
       </c>
     </row>
-    <row r="336" spans="1:3">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
-        <v>44128</v>
+        <v>45589</v>
       </c>
       <c r="B336" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C336">
         <v>33</v>
       </c>
     </row>
-    <row r="337" spans="1:3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
-        <v>44128</v>
+        <v>45589</v>
       </c>
       <c r="B337" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C337">
         <v>41</v>
       </c>
     </row>
-    <row r="338" spans="1:3">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" s="2">
-        <v>44128</v>
+        <v>45589</v>
       </c>
       <c r="B338" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C338">
         <v>72</v>
       </c>
     </row>
-    <row r="339" spans="1:3">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" s="2">
-        <v>44128</v>
+        <v>45589</v>
       </c>
       <c r="B339" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C339">
         <v>35</v>
       </c>
     </row>
-    <row r="340" spans="1:3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" s="2">
-        <v>44128</v>
+        <v>45589</v>
       </c>
       <c r="B340" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C340">
         <v>37</v>
       </c>
     </row>
-    <row r="341" spans="1:3">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" s="2">
-        <v>44128</v>
+        <v>45589</v>
       </c>
       <c r="B341" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C341">
         <v>64</v>
       </c>
     </row>
-    <row r="342" spans="1:3">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" s="2">
-        <v>44135</v>
+        <v>45596</v>
       </c>
       <c r="B342" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C342">
         <v>39</v>
       </c>
     </row>
-    <row r="343" spans="1:3">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="2">
-        <v>44135</v>
+        <v>45596</v>
       </c>
       <c r="B343" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C343">
         <v>36</v>
       </c>
     </row>
-    <row r="344" spans="1:3">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" s="2">
-        <v>44135</v>
+        <v>45596</v>
       </c>
       <c r="B344" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C344">
         <v>31</v>
       </c>
     </row>
-    <row r="345" spans="1:3">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" s="2">
-        <v>44135</v>
+        <v>45596</v>
       </c>
       <c r="B345" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C345">
         <v>32</v>
       </c>
     </row>
-    <row r="346" spans="1:3">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" s="2">
-        <v>44135</v>
+        <v>45596</v>
       </c>
       <c r="B346" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C346">
         <v>49</v>
       </c>
     </row>
-    <row r="347" spans="1:3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" s="2">
-        <v>44142</v>
+        <v>45603</v>
       </c>
       <c r="B347" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C347">
         <v>42</v>
       </c>
     </row>
-    <row r="348" spans="1:3">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" s="2">
-        <v>44142</v>
+        <v>45603</v>
       </c>
       <c r="B348" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C348">
         <v>50</v>
       </c>
     </row>
-    <row r="349" spans="1:3">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" s="2">
-        <v>44142</v>
+        <v>45603</v>
       </c>
       <c r="B349" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C349">
         <v>72</v>
       </c>
     </row>
-    <row r="350" spans="1:3">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
-        <v>44142</v>
+        <v>45603</v>
       </c>
       <c r="B350" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C350">
         <v>39</v>
       </c>
     </row>
-    <row r="351" spans="1:3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
-        <v>44142</v>
+        <v>45603</v>
       </c>
       <c r="B351" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C351">
         <v>38</v>
       </c>
     </row>
-    <row r="352" spans="1:3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
-        <v>44142</v>
+        <v>45603</v>
       </c>
       <c r="B352" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C352">
         <v>63</v>
       </c>
     </row>
-    <row r="353" spans="1:3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
-        <v>44149</v>
+        <v>45610</v>
       </c>
       <c r="B353" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C353">
         <v>53</v>
       </c>
     </row>
-    <row r="354" spans="1:3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
-        <v>44149</v>
+        <v>45610</v>
       </c>
       <c r="B354" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C354">
         <v>57</v>
       </c>
     </row>
-    <row r="355" spans="1:3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
-        <v>44149</v>
+        <v>45610</v>
       </c>
       <c r="B355" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C355">
         <v>42</v>
       </c>
     </row>
-    <row r="356" spans="1:3">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
-        <v>44149</v>
+        <v>45610</v>
       </c>
       <c r="B356" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C356">
         <v>41</v>
       </c>
     </row>
-    <row r="357" spans="1:3">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
-        <v>44149</v>
+        <v>45610</v>
       </c>
       <c r="B357" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C357">
         <v>64</v>
       </c>
     </row>
-    <row r="358" spans="1:3">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
-        <v>44156</v>
+        <v>45617</v>
       </c>
       <c r="B358" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C358">
         <v>53</v>
       </c>
     </row>
-    <row r="359" spans="1:3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
-        <v>44156</v>
+        <v>45617</v>
       </c>
       <c r="B359" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C359">
         <v>100</v>
       </c>
     </row>
-    <row r="360" spans="1:3">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
-        <v>44156</v>
+        <v>45617</v>
       </c>
       <c r="B360" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C360">
         <v>33</v>
       </c>
     </row>
-    <row r="361" spans="1:3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
-        <v>44156</v>
+        <v>45617</v>
       </c>
       <c r="B361" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C361">
         <v>53</v>
       </c>
     </row>
-    <row r="362" spans="1:3">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A362" s="2">
-        <v>44156</v>
+        <v>45617</v>
       </c>
       <c r="B362" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C362">
         <v>61</v>
       </c>
     </row>
-    <row r="363" spans="1:3">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363" s="2">
-        <v>44163</v>
+        <v>45624</v>
       </c>
       <c r="B363" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C363">
         <v>46</v>
       </c>
     </row>
-    <row r="364" spans="1:3">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A364" s="2">
-        <v>44163</v>
+        <v>45624</v>
       </c>
       <c r="B364" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C364">
         <v>91</v>
       </c>
     </row>
-    <row r="365" spans="1:3">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="2">
-        <v>44163</v>
+        <v>45624</v>
       </c>
       <c r="B365" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C365">
         <v>76</v>
       </c>
     </row>
-    <row r="366" spans="1:3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A366" s="2">
-        <v>44163</v>
+        <v>45624</v>
       </c>
       <c r="B366" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C366">
         <v>38</v>
       </c>
     </row>
-    <row r="367" spans="1:3">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A367" s="2">
-        <v>44163</v>
+        <v>45624</v>
       </c>
       <c r="B367" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C367">
         <v>41</v>
       </c>
     </row>
-    <row r="368" spans="1:3">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A368" s="2">
-        <v>44163</v>
+        <v>45624</v>
       </c>
       <c r="B368" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C368">
         <v>57</v>
       </c>
     </row>
-    <row r="369" spans="1:3">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369" s="2">
-        <v>44170</v>
+        <v>45631</v>
       </c>
       <c r="B369" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C369">
         <v>32</v>
       </c>
     </row>
-    <row r="370" spans="1:3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A370" s="2">
-        <v>44170</v>
+        <v>45631</v>
       </c>
       <c r="B370" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C370">
         <v>40</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371" s="2">
-        <v>44170</v>
+        <v>45631</v>
       </c>
       <c r="B371" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C371">
         <v>59</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A372" s="2">
-        <v>44177</v>
+        <v>45638</v>
       </c>
       <c r="B372" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C372">
         <v>46</v>
       </c>
     </row>
-    <row r="373" spans="1:3">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373" s="2">
-        <v>44177</v>
+        <v>45638</v>
       </c>
       <c r="B373" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C373">
         <v>55</v>
       </c>
     </row>
-    <row r="374" spans="1:3">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
-        <v>44177</v>
+        <v>45638</v>
       </c>
       <c r="B374" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C374">
         <v>71</v>
       </c>
     </row>
-    <row r="375" spans="1:3">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
-        <v>44177</v>
+        <v>45638</v>
       </c>
       <c r="B375" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C375">
         <v>47</v>
       </c>
     </row>
-    <row r="376" spans="1:3">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
-        <v>44177</v>
+        <v>45638</v>
       </c>
       <c r="B376" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C376">
         <v>62</v>
       </c>
     </row>
-    <row r="377" spans="1:3">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
-        <v>44184</v>
+        <v>45645</v>
       </c>
       <c r="B377" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C377">
         <v>24</v>
       </c>
     </row>
-    <row r="378" spans="1:3">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
-        <v>44184</v>
+        <v>45645</v>
       </c>
       <c r="B378" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C378">
         <v>60</v>
       </c>
     </row>
-    <row r="379" spans="1:3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
-        <v>44184</v>
+        <v>45645</v>
       </c>
       <c r="B379" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C379">
         <v>48</v>
       </c>
     </row>
-    <row r="380" spans="1:3">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
-        <v>44184</v>
+        <v>45645</v>
       </c>
       <c r="B380" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C380">
         <v>68</v>
       </c>
     </row>
-    <row r="381" spans="1:3">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
-        <v>44191</v>
+        <v>45652</v>
       </c>
       <c r="B381" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C381">
         <v>45</v>
       </c>
     </row>
-    <row r="382" spans="1:3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
-        <v>44191</v>
+        <v>45652</v>
       </c>
       <c r="B382" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C382">
         <v>64</v>
       </c>
     </row>
-    <row r="383" spans="1:3">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
-        <v>44191</v>
+        <v>45652</v>
       </c>
       <c r="B383" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C383">
         <v>44</v>
       </c>
     </row>
-    <row r="384" spans="1:3">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
-        <v>44191</v>
+        <v>45652</v>
       </c>
       <c r="B384" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C384">
         <v>79</v>
       </c>
     </row>
-    <row r="385" spans="1:3">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
-        <v>44198</v>
+        <v>45659</v>
       </c>
       <c r="B385" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C385">
         <v>78</v>
       </c>
     </row>
-    <row r="386" spans="1:3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A386" s="2">
-        <v>44198</v>
+        <v>45659</v>
       </c>
       <c r="B386" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C386">
         <v>46</v>
       </c>
     </row>
-    <row r="387" spans="1:3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="2">
-        <v>44198</v>
+        <v>45659</v>
       </c>
       <c r="B387" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C387">
         <v>37</v>
       </c>
     </row>
-    <row r="388" spans="1:3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A388" s="2">
-        <v>44198</v>
+        <v>45659</v>
       </c>
       <c r="B388" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C388">
         <v>32</v>
       </c>
     </row>
-    <row r="389" spans="1:3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A389" s="2">
-        <v>44198</v>
+        <v>45659</v>
       </c>
       <c r="B389" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C389">
         <v>62</v>
       </c>
     </row>
-    <row r="390" spans="1:3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A390" s="2">
-        <v>44205</v>
+        <v>45666</v>
       </c>
       <c r="B390" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C390">
         <v>73</v>
       </c>
     </row>
-    <row r="391" spans="1:3">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A391" s="2">
-        <v>44205</v>
+        <v>45666</v>
       </c>
       <c r="B391" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C391">
         <v>41</v>
       </c>
     </row>
-    <row r="392" spans="1:3">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A392" s="2">
-        <v>44205</v>
+        <v>45666</v>
       </c>
       <c r="B392" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C392">
         <v>40</v>
       </c>
     </row>
-    <row r="393" spans="1:3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A393" s="2">
-        <v>44205</v>
+        <v>45666</v>
       </c>
       <c r="B393" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C393">
         <v>32</v>
       </c>
     </row>
-    <row r="394" spans="1:3">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A394" s="2">
-        <v>44205</v>
+        <v>45666</v>
       </c>
       <c r="B394" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C394">
         <v>69</v>
       </c>
     </row>
-    <row r="395" spans="1:3">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A395" s="2">
-        <v>44212</v>
+        <v>45673</v>
       </c>
       <c r="B395" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C395">
         <v>86</v>
       </c>
     </row>
-    <row r="396" spans="1:3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A396" s="2">
-        <v>44212</v>
+        <v>45673</v>
       </c>
       <c r="B396" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C396">
         <v>32</v>
       </c>
     </row>
-    <row r="397" spans="1:3">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A397" s="2">
-        <v>44212</v>
+        <v>45673</v>
       </c>
       <c r="B397" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C397">
         <v>69</v>
       </c>
     </row>
-    <row r="398" spans="1:3">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
-        <v>44219</v>
+        <v>45680</v>
       </c>
       <c r="B398" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C398">
         <v>76</v>
       </c>
     </row>
-    <row r="399" spans="1:3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
-        <v>44219</v>
+        <v>45680</v>
       </c>
       <c r="B399" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C399">
         <v>49</v>
       </c>
     </row>
-    <row r="400" spans="1:3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
-        <v>44219</v>
+        <v>45680</v>
       </c>
       <c r="B400" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C400">
         <v>32</v>
       </c>
     </row>
-    <row r="401" spans="1:3">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
-        <v>44219</v>
+        <v>45680</v>
       </c>
       <c r="B401" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C401">
         <v>70</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
-        <v>44226</v>
+        <v>45687</v>
       </c>
       <c r="B402" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C402">
         <v>69</v>
       </c>
     </row>
-    <row r="403" spans="1:3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
-        <v>44226</v>
+        <v>45687</v>
       </c>
       <c r="B403" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C403">
         <v>45</v>
       </c>
     </row>
-    <row r="404" spans="1:3">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
-        <v>44226</v>
+        <v>45687</v>
       </c>
       <c r="B404" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C404">
         <v>40</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
-        <v>44226</v>
+        <v>45687</v>
       </c>
       <c r="B405" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C405">
         <v>30</v>
       </c>
     </row>
-    <row r="406" spans="1:3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
-        <v>44226</v>
+        <v>45687</v>
       </c>
       <c r="B406" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C406">
         <v>65</v>
       </c>
     </row>
-    <row r="407" spans="1:3">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
-        <v>44233</v>
+        <v>45694</v>
       </c>
       <c r="B407" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C407">
         <v>56</v>
       </c>
     </row>
-    <row r="408" spans="1:3">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
-        <v>44233</v>
+        <v>45694</v>
       </c>
       <c r="B408" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C408">
         <v>42</v>
       </c>
     </row>
-    <row r="409" spans="1:3">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
-        <v>44233</v>
+        <v>45694</v>
       </c>
       <c r="B409" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C409">
         <v>58</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A410" s="2">
-        <v>44233</v>
+        <v>45694</v>
       </c>
       <c r="B410" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C410">
         <v>38</v>
       </c>
     </row>
-    <row r="411" spans="1:3">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A411" s="2">
-        <v>44233</v>
+        <v>45694</v>
       </c>
       <c r="B411" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C411">
         <v>71</v>
       </c>
     </row>
-    <row r="412" spans="1:3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A412" s="2">
-        <v>44240</v>
+        <v>45701</v>
       </c>
       <c r="B412" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C412">
         <v>44</v>
       </c>
     </row>
-    <row r="413" spans="1:3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A413" s="2">
-        <v>44240</v>
+        <v>45701</v>
       </c>
       <c r="B413" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C413">
         <v>40</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A414" s="2">
-        <v>44240</v>
+        <v>45701</v>
       </c>
       <c r="B414" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C414">
         <v>42</v>
       </c>
     </row>
-    <row r="415" spans="1:3">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A415" s="2">
-        <v>44240</v>
+        <v>45701</v>
       </c>
       <c r="B415" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C415">
         <v>78</v>
       </c>
     </row>
-    <row r="416" spans="1:3">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A416" s="2">
-        <v>44247</v>
+        <v>45708</v>
       </c>
       <c r="B416" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C416">
         <v>82</v>
       </c>
     </row>
-    <row r="417" spans="1:3">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A417" s="2">
-        <v>44247</v>
+        <v>45708</v>
       </c>
       <c r="B417" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C417">
         <v>40</v>
       </c>
     </row>
-    <row r="418" spans="1:3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A418" s="2">
-        <v>44247</v>
+        <v>45708</v>
       </c>
       <c r="B418" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C418">
         <v>38</v>
       </c>
     </row>
-    <row r="419" spans="1:3">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A419" s="2">
-        <v>44247</v>
+        <v>45708</v>
       </c>
       <c r="B419" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C419">
         <v>100</v>
       </c>
     </row>
-    <row r="420" spans="1:3">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="2">
-        <v>44254</v>
+        <v>45715</v>
       </c>
       <c r="B420" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C420">
         <v>71</v>
       </c>
     </row>
-    <row r="421" spans="1:3">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A421" s="2">
-        <v>44254</v>
+        <v>45715</v>
       </c>
       <c r="B421" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C421">
         <v>47</v>
       </c>
     </row>
-    <row r="422" spans="1:3">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
-        <v>44254</v>
+        <v>45715</v>
       </c>
       <c r="B422" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C422">
         <v>34</v>
       </c>
     </row>
-    <row r="423" spans="1:3">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
-        <v>44254</v>
+        <v>45715</v>
       </c>
       <c r="B423" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C423">
         <v>84</v>
       </c>
     </row>
-    <row r="424" spans="1:3">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
-        <v>44261</v>
+        <v>45722</v>
       </c>
       <c r="B424" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C424">
         <v>61</v>
       </c>
     </row>
-    <row r="425" spans="1:3">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
-        <v>44261</v>
+        <v>45722</v>
       </c>
       <c r="B425" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C425">
         <v>50</v>
       </c>
     </row>
-    <row r="426" spans="1:3">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
-        <v>44261</v>
+        <v>45722</v>
       </c>
       <c r="B426" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C426">
         <v>46</v>
       </c>
     </row>
-    <row r="427" spans="1:3">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A427" s="2">
-        <v>44261</v>
+        <v>45722</v>
       </c>
       <c r="B427" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C427">
         <v>82</v>
       </c>
     </row>
-    <row r="428" spans="1:3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A428" s="2">
-        <v>44268</v>
+        <v>45729</v>
       </c>
       <c r="B428" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C428">
         <v>67</v>
       </c>
     </row>
-    <row r="429" spans="1:3">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A429" s="2">
-        <v>44268</v>
+        <v>45729</v>
       </c>
       <c r="B429" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C429">
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:3">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A430" s="2">
-        <v>44268</v>
+        <v>45729</v>
       </c>
       <c r="B430" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C430">
         <v>83</v>
       </c>
     </row>
-    <row r="431" spans="1:3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="2">
-        <v>44275</v>
+        <v>45736</v>
       </c>
       <c r="B431" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C431">
         <v>65</v>
       </c>
     </row>
-    <row r="432" spans="1:3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A432" s="2">
-        <v>44275</v>
+        <v>45736</v>
       </c>
       <c r="B432" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C432">
         <v>36</v>
       </c>
     </row>
-    <row r="433" spans="1:3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A433" s="2">
-        <v>44275</v>
+        <v>45736</v>
       </c>
       <c r="B433" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C433">
         <v>50</v>
       </c>
     </row>
-    <row r="434" spans="1:3">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A434" s="2">
-        <v>44275</v>
+        <v>45736</v>
       </c>
       <c r="B434" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C434">
         <v>83</v>
       </c>
     </row>
-    <row r="435" spans="1:3">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A435" s="2">
-        <v>44282</v>
+        <v>45743</v>
       </c>
       <c r="B435" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C435">
         <v>56</v>
       </c>
     </row>
-    <row r="436" spans="1:3">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A436" s="2">
-        <v>44282</v>
+        <v>45743</v>
       </c>
       <c r="B436" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C436">
         <v>72</v>
       </c>
     </row>
-    <row r="437" spans="1:3">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A437" s="2">
-        <v>44282</v>
+        <v>45743</v>
       </c>
       <c r="B437" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C437">
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:3">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A438" s="2">
-        <v>44282</v>
+        <v>45743</v>
       </c>
       <c r="B438" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C438">
         <v>81</v>
       </c>
     </row>
-    <row r="439" spans="1:3">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A439" s="2">
-        <v>44289</v>
+        <v>45750</v>
       </c>
       <c r="B439" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C439">
         <v>87</v>
       </c>
     </row>
-    <row r="440" spans="1:3">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A440" s="2">
-        <v>44289</v>
+        <v>45750</v>
       </c>
       <c r="B440" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C440">
         <v>55</v>
       </c>
     </row>
-    <row r="441" spans="1:3">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A441" s="2">
-        <v>44289</v>
+        <v>45750</v>
       </c>
       <c r="B441" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C441">
         <v>52</v>
       </c>
     </row>
-    <row r="442" spans="1:3">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="2">
-        <v>44289</v>
+        <v>45750</v>
       </c>
       <c r="B442" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C442">
         <v>84</v>
       </c>
     </row>
-    <row r="443" spans="1:3">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A443" s="2">
-        <v>44296</v>
+        <v>45757</v>
       </c>
       <c r="B443" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C443">
         <v>100</v>
       </c>
     </row>
-    <row r="444" spans="1:3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A444" s="2">
-        <v>44296</v>
+        <v>45757</v>
       </c>
       <c r="B444" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C444">
         <v>49</v>
       </c>
     </row>
-    <row r="445" spans="1:3">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A445" s="2">
-        <v>44296</v>
+        <v>45757</v>
       </c>
       <c r="B445" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C445">
         <v>51</v>
       </c>
     </row>
-    <row r="446" spans="1:3">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A446" s="2">
-        <v>44296</v>
+        <v>45757</v>
       </c>
       <c r="B446" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C446">
         <v>82</v>
       </c>
     </row>
-    <row r="447" spans="1:3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A447" s="2">
-        <v>44303</v>
+        <v>45764</v>
       </c>
       <c r="B447" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C447">
         <v>77</v>
       </c>
     </row>
-    <row r="448" spans="1:3">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A448" s="2">
-        <v>44303</v>
+        <v>45764</v>
       </c>
       <c r="B448" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C448">
         <v>48</v>
       </c>
     </row>
-    <row r="449" spans="1:3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A449" s="2">
-        <v>44303</v>
+        <v>45764</v>
       </c>
       <c r="B449" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C449">
         <v>46</v>
       </c>
     </row>
-    <row r="450" spans="1:3">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A450" s="2">
-        <v>44303</v>
+        <v>45764</v>
       </c>
       <c r="B450" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C450">
         <v>85</v>
       </c>
     </row>
-    <row r="451" spans="1:3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A451" s="2">
-        <v>44310</v>
+        <v>45771</v>
       </c>
       <c r="B451" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C451">
         <v>80</v>
       </c>
     </row>
-    <row r="452" spans="1:3">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A452" s="2">
-        <v>44310</v>
+        <v>45771</v>
       </c>
       <c r="B452" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C452">
         <v>47</v>
       </c>
     </row>
-    <row r="453" spans="1:3">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="2">
-        <v>44310</v>
+        <v>45771</v>
       </c>
       <c r="B453" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C453">
         <v>43</v>
       </c>
     </row>
-    <row r="454" spans="1:3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A454" s="2">
-        <v>44310</v>
+        <v>45771</v>
       </c>
       <c r="B454" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C454">
         <v>77</v>
       </c>
     </row>
-    <row r="455" spans="1:3">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A455" s="2">
-        <v>44317</v>
+        <v>45778</v>
       </c>
       <c r="B455" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C455">
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:3">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A456" s="2">
-        <v>44317</v>
+        <v>45778</v>
       </c>
       <c r="B456" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C456">
         <v>38</v>
       </c>
     </row>
-    <row r="457" spans="1:3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A457" s="2">
-        <v>44317</v>
+        <v>45778</v>
       </c>
       <c r="B457" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C457">
         <v>52</v>
       </c>
     </row>
-    <row r="458" spans="1:3">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A458" s="2">
-        <v>44317</v>
+        <v>45778</v>
       </c>
       <c r="B458" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C458">
         <v>41</v>
       </c>
     </row>
-    <row r="459" spans="1:3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A459" s="2">
-        <v>44317</v>
+        <v>45778</v>
       </c>
       <c r="B459" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C459">
         <v>76</v>
       </c>
     </row>
-    <row r="460" spans="1:3">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A460" s="2">
-        <v>44324</v>
+        <v>45785</v>
       </c>
       <c r="B460" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C460">
         <v>70</v>
       </c>
     </row>
-    <row r="461" spans="1:3">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A461" s="2">
-        <v>44324</v>
+        <v>45785</v>
       </c>
       <c r="B461" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C461">
         <v>39</v>
       </c>
     </row>
-    <row r="462" spans="1:3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A462" s="2">
-        <v>44324</v>
+        <v>45785</v>
       </c>
       <c r="B462" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C462">
         <v>51</v>
       </c>
     </row>
-    <row r="463" spans="1:3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A463" s="2">
-        <v>44324</v>
+        <v>45785</v>
       </c>
       <c r="B463" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C463">
         <v>46</v>
       </c>
     </row>
-    <row r="464" spans="1:3">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="2">
-        <v>44324</v>
+        <v>45785</v>
       </c>
       <c r="B464" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C464">
         <v>80</v>
       </c>
     </row>
-    <row r="465" spans="1:3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A465" s="2">
-        <v>44331</v>
+        <v>45792</v>
       </c>
       <c r="B465" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C465">
         <v>67</v>
       </c>
     </row>
-    <row r="466" spans="1:3">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A466" s="2">
-        <v>44331</v>
+        <v>45792</v>
       </c>
       <c r="B466" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C466">
         <v>42</v>
       </c>
     </row>
-    <row r="467" spans="1:3">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A467" s="2">
-        <v>44331</v>
+        <v>45792</v>
       </c>
       <c r="B467" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C467">
         <v>54</v>
       </c>
     </row>
-    <row r="468" spans="1:3">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A468" s="2">
-        <v>44331</v>
+        <v>45792</v>
       </c>
       <c r="B468" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C468">
         <v>31</v>
       </c>
     </row>
-    <row r="469" spans="1:3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A469" s="2">
-        <v>44331</v>
+        <v>45792</v>
       </c>
       <c r="B469" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C469">
         <v>86</v>
       </c>
     </row>
-    <row r="470" spans="1:3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A470" s="2">
-        <v>44338</v>
+        <v>45799</v>
       </c>
       <c r="B470" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C470">
         <v>60</v>
       </c>
     </row>
-    <row r="471" spans="1:3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A471" s="2">
-        <v>44338</v>
+        <v>45799</v>
       </c>
       <c r="B471" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C471">
         <v>45</v>
       </c>
     </row>
-    <row r="472" spans="1:3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A472" s="2">
-        <v>44338</v>
+        <v>45799</v>
       </c>
       <c r="B472" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C472">
         <v>52</v>
       </c>
     </row>
-    <row r="473" spans="1:3">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A473" s="2">
-        <v>44338</v>
+        <v>45799</v>
       </c>
       <c r="B473" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C473">
         <v>30</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A474" s="2">
-        <v>44338</v>
+        <v>45799</v>
       </c>
       <c r="B474" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C474">
         <v>85</v>
@@ -5639,6 +5642,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dfb62c77-32f9-4cef-8886-9e57b7381c9d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4031e5ff-f3c5-423c-8fab-1d57f6a3be94" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001D85B782F009BA4A8051764404D1F46A" ma:contentTypeVersion="17" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="aeb43e99c2d936b97eb387d5eb102981">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dfb62c77-32f9-4cef-8886-9e57b7381c9d" xmlns:ns3="4031e5ff-f3c5-423c-8fab-1d57f6a3be94" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7799380c5bffed07a89ef908f557d0dc" ns2:_="" ns3:_="">
     <xsd:import namespace="dfb62c77-32f9-4cef-8886-9e57b7381c9d"/>
@@ -5887,34 +5910,52 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="dfb62c77-32f9-4cef-8886-9e57b7381c9d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4031e5ff-f3c5-423c-8fab-1d57f6a3be94" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{477700E1-D27D-4134-A4B0-E8B76A6AB249}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26E61A38-6461-4986-8B3A-3271E4EA107B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="4031e5ff-f3c5-423c-8fab-1d57f6a3be94"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dfb62c77-32f9-4cef-8886-9e57b7381c9d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2690479-14DF-498E-9EC8-7DAEF2C3BAA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2690479-14DF-498E-9EC8-7DAEF2C3BAA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26E61A38-6461-4986-8B3A-3271E4EA107B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{477700E1-D27D-4134-A4B0-E8B76A6AB249}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="dfb62c77-32f9-4cef-8886-9e57b7381c9d"/>
+    <ds:schemaRef ds:uri="4031e5ff-f3c5-423c-8fab-1d57f6a3be94"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a7262e59-1b56-4f5a-a412-6f07181f48ee}" enabled="0" method="" siteId="{a7262e59-1b56-4f5a-a412-6f07181f48ee}" removed="1"/>
+</clbl:labelList>
 </file>